--- a/nomination_forms/016_outstanding_young_alumni_recognition_nomination--nomination_forms.xlsx
+++ b/nomination_forms/016_outstanding_young_alumni_recognition_nomination--nomination_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -579,7 +579,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>university_name</t>
+          <t>university_name_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nominee_name</t>
+          <t>nominee_name_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nominee Name</t>
+          <t>Nominee Name 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nominee_contact_email</t>
+          <t>nominee_contact_email_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nominee Email</t>
+          <t>Nominee Contact Email 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nominator_name</t>
+          <t>nominator_name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nominator Name</t>
+          <t>Nominator Name 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nominator_contact_email</t>
+          <t>nominator_contact_email_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nominator Email</t>
+          <t>Nominator Contact Email 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
